--- a/Packages/cn.etetet.yiuiluban/.Template/cn.etetet.yiui/Editor/Luban/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuiluban/.Template/cn.etetet.yiui/Editor/Luban/Base/__tables__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="25185" windowHeight="13890"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="YIUI" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,12 @@
     <t>输出文件名</t>
   </si>
   <si>
+    <t>包名</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
     <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
   </si>
   <si>
@@ -108,6 +114,12 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>yiuilubangen</t>
+  </si>
+  <si>
+    <t>Demo</t>
   </si>
 </sst>
 </file>
@@ -723,11 +735,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,6 +804,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,91 +1071,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.575" customWidth="1"/>
-    <col min="4" max="4" width="32.425" customWidth="1"/>
-    <col min="5" max="5" width="24.3833333333333" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="3" width="29.375" customWidth="1"/>
+    <col min="4" max="4" width="51.5" customWidth="1"/>
+    <col min="5" max="5" width="32.625" customWidth="1"/>
+    <col min="6" max="6" width="27.875" customWidth="1"/>
+    <col min="7" max="7" width="82.375" customWidth="1"/>
+    <col min="8" max="11" width="16.5" customWidth="1"/>
+    <col min="12" max="12" width="25.625" customWidth="1"/>
+    <col min="13" max="13" width="49.875" customWidth="1"/>
+    <col min="14" max="16384" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1145,13 +1176,48 @@
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:13">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="str">
+        <f>_xlfn.CONCAT("cn.etetet.",B4,".",C4,"ConfigCategory")</f>
+        <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
+      </c>
+      <c r="E4" t="str">
+        <f>_xlfn.CONCAT(C4,"Config")</f>
+        <v>DemoConfig</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="str">
+        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
+      </c>
+      <c r="M4" t="str">
+        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <v>DemoConfigCategory</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>